--- a/master Quotations_October_2026/Estimates_ For barbendind & cutting & Vibrator machines and_Quotations_Summary.xlsx
+++ b/master Quotations_October_2026/Estimates_ For barbendind & cutting & Vibrator machines and_Quotations_Summary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\Purchase_List_October_2026\master Quotations_October_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F94C85-A683-48D9-B9BB-920288F9CEF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1956DE-772A-40B3-BB62-74F746442C5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="96">
   <si>
     <t>ESTIMATE DETAILS</t>
   </si>
@@ -332,6 +332,9 @@
   </si>
   <si>
     <t>• Transportation: Extra</t>
+  </si>
+  <si>
+    <t>APPROVED THIS QUOTATION</t>
   </si>
 </sst>
 </file>
@@ -342,7 +345,7 @@
     <numFmt numFmtId="164" formatCode="&quot;₹ &quot;#,##0.00"/>
     <numFmt numFmtId="165" formatCode="\₹#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -404,8 +407,22 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -436,8 +453,14 @@
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -471,11 +494,122 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -496,62 +630,762 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="35">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF2F5597"/>
+          <bgColor rgb="FF2F5597"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF595959"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF1F497D"/>
+          <bgColor rgb="FF1F497D"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -562,6 +1396,70 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{CF3D2F99-5225-477D-A6D5-652C512EA996}" name="Table3" displayName="Table3" ref="A11:H21" totalsRowShown="0" headerRowDxfId="23" headerRowBorderDxfId="33" tableBorderDxfId="34" totalsRowBorderDxfId="32">
+  <autoFilter ref="A11:H21" xr:uid="{CF3D2F99-5225-477D-A6D5-652C512EA996}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{5EEED208-E551-4E8D-9DB3-7C5DF4773138}" name="S No" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{5F074C90-5851-4C4D-ABCF-3D66E08BD569}" name="Item Name" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{B3D18E6C-651C-4A22-8244-26922C1ACDD9}" name="HSN/SAC" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{F26C0A8C-DE83-4BA4-A47D-FA94A9D1B4A5}" name="Quantity" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{12A2BF8C-33D0-4F8B-9B70-674674A0A6EC}" name="Unit" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{43E5E670-77A3-4311-A2F3-9819A3DD959B}" name="Price/Unit" dataDxfId="26"/>
+    <tableColumn id="7" xr3:uid="{DDA6E310-69AE-40D1-9CEB-5EF75908058F}" name="GST" dataDxfId="25"/>
+    <tableColumn id="8" xr3:uid="{1436B8EF-8EAB-4356-A9F2-6DD4443CC9D0}" name="Amount" dataDxfId="24"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{C837F009-5EE4-4F33-99F0-9881D7406E33}" name="Table4" displayName="Table4" ref="A11:F17" totalsRowShown="0" headerRowDxfId="19" dataDxfId="12" headerRowBorderDxfId="21" tableBorderDxfId="22" totalsRowBorderDxfId="20">
+  <autoFilter ref="A11:F17" xr:uid="{C837F009-5EE4-4F33-99F0-9881D7406E33}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{1D5EE62C-3F10-4738-B900-D495835A7E15}" name="S.No." dataDxfId="18"/>
+    <tableColumn id="2" xr3:uid="{0B68D1BC-13AF-48F6-9F7C-30D6B0ACBBDF}" name="Item Code" dataDxfId="17"/>
+    <tableColumn id="3" xr3:uid="{55F696FA-2145-443B-ABE3-2AD7BBB55A18}" name="Item Details" dataDxfId="16"/>
+    <tableColumn id="4" xr3:uid="{BD103DFC-A757-4B16-B0EA-B89CD8EA39E9}" name="Quantity" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{AA56915F-8535-4068-8037-EFEBB66E78A5}" name="Price" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{9ACA4EB6-64ED-44A0-82EA-A9CA9E52D754}" name="Total" dataDxfId="13"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{EE954F4B-FE3D-415C-99E2-B626A809F761}" name="Table5" displayName="Table5" ref="A11:G20" totalsRowShown="0" headerRowDxfId="11">
+  <autoFilter ref="A11:G20" xr:uid="{EE954F4B-FE3D-415C-99E2-B626A809F761}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{8B0FD278-B0BD-4778-A4BA-DBBBFD9E3C85}" name="Sl No."/>
+    <tableColumn id="2" xr3:uid="{89027179-7412-4549-AFE9-4C66CBD2CFBC}" name="Description of Goods"/>
+    <tableColumn id="3" xr3:uid="{303C4B82-5F6B-46D2-B540-1126704D18CF}" name="HSN/SAC"/>
+    <tableColumn id="4" xr3:uid="{14960879-6B19-4CBE-9D43-67820B0C03CC}" name="GST Rate"/>
+    <tableColumn id="5" xr3:uid="{BCA48CA9-FB19-4BC8-A8FC-6BC8205A77D4}" name="Quantity"/>
+    <tableColumn id="6" xr3:uid="{E715DE5B-FD06-476F-97C3-33D070BF6092}" name="Rate per"/>
+    <tableColumn id="7" xr3:uid="{F6DCD94B-78F4-4FBD-82C4-11DE5F29C1F6}" name="Amount"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{39A7C464-9B18-438F-BAED-F60681931F5C}" name="Table7" displayName="Table7" ref="A3:G16" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="10" totalsRowBorderDxfId="8">
+  <autoFilter ref="A3:G16" xr:uid="{39A7C464-9B18-438F-BAED-F60681931F5C}"/>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{30725AE4-2789-48A4-8CF9-C878C1879556}" name="S.No." dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{C28BFD16-DF0D-4DA0-BB1D-C3EEF425F702}" name="Item Description / Specifications" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{CF1BDB38-EB88-4ED4-AE89-109835D20D61}" name="Model/Code" dataDxfId="5"/>
+    <tableColumn id="4" xr3:uid="{A9A15F4A-15DF-4862-B148-BD879E134D07}" name="Qty" dataDxfId="4"/>
+    <tableColumn id="5" xr3:uid="{F746729E-52B0-43E8-8CBA-EF83B6E4465E}" name="Original Price" dataDxfId="3"/>
+    <tableColumn id="6" xr3:uid="{A92FAFD7-4C66-4CE8-B980-BC8D433A4C46}" name="Discounted Price" dataDxfId="2"/>
+    <tableColumn id="7" xr3:uid="{E69DB772-8235-44EE-BBA4-A461EF88262C}" name="Total (Excl. GST)" dataDxfId="1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -849,225 +1747,344 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
     <col min="2" max="2" width="71.28515625" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="17" customWidth="1"/>
+    <col min="5" max="5" width="19.85546875" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3" spans="1:8" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14" t="s">
         <v>2</v>
       </c>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13" t="s">
         <v>4</v>
       </c>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E5" t="s">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13" t="s">
         <v>6</v>
       </c>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="13" t="s">
         <v>7</v>
       </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="64" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="65"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="13" t="s">
         <v>8</v>
       </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="4">
+      <c r="B9" s="16">
         <v>457</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="23" t="s">
         <v>11</v>
       </c>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
     </row>
     <row r="11" spans="1:8" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="35" t="s">
         <v>74</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="36" t="s">
         <v>13</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="37" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="27">
         <v>1</v>
       </c>
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18">
         <v>1</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="19">
         <v>66000</v>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="19">
         <v>11880</v>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="29">
         <v>77880</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="27">
         <v>2</v>
       </c>
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18">
         <v>1</v>
       </c>
-      <c r="E13" s="7" t="s">
+      <c r="E13" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="19">
         <v>59000</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="19">
         <v>10620</v>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="29">
         <v>69620</v>
       </c>
     </row>
     <row r="14" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="27">
         <v>3</v>
       </c>
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7">
+      <c r="C14" s="18"/>
+      <c r="D14" s="18">
         <v>1</v>
       </c>
-      <c r="E14" s="7" t="s">
+      <c r="E14" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="19">
         <v>17600</v>
       </c>
-      <c r="G14" s="13">
+      <c r="G14" s="19">
         <v>3168</v>
       </c>
-      <c r="H14" s="13">
+      <c r="H14" s="29">
         <v>20768</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="15" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="20"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="16">
+      <c r="H15" s="30">
         <v>142600</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="15" t="s">
+      <c r="A16" s="25"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="H16" s="16">
+      <c r="H16" s="30">
         <v>12834</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="15" t="s">
+      <c r="A17" s="25"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="F17" s="20"/>
+      <c r="G17" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="H17" s="16">
+      <c r="H17" s="30">
         <v>12834</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="17" t="s">
+      <c r="A18" s="25"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="H18" s="18">
+      <c r="H18" s="31">
         <f>SUM(H15:H17)</f>
         <v>168268</v>
       </c>
     </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="25"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="28"/>
+    </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="17" t="s">
         <v>28</v>
       </c>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
+      <c r="H20" s="28"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="34"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E6:F7"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1078,168 +2095,237 @@
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="45" customWidth="1"/>
-    <col min="3" max="3" width="53.7109375" customWidth="1"/>
+    <col min="3" max="3" width="59.28515625" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="6" width="17" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="12" t="s">
         <v>29</v>
       </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="3" spans="1:6" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="14" t="s">
         <v>2</v>
       </c>
+      <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13" t="s">
         <v>31</v>
       </c>
+      <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="13" t="s">
         <v>32</v>
       </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" s="13" t="s">
         <v>33</v>
       </c>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" s="13" t="s">
         <v>34</v>
       </c>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="23" t="s">
         <v>37</v>
       </c>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="13"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+    </row>
     <row r="11" spans="1:6" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="35" t="s">
         <v>38</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="36" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="36" t="s">
         <v>40</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="36" t="s">
         <v>41</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="37" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
+      <c r="A12" s="38">
         <v>1</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="40" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="7">
+      <c r="D12" s="39">
         <v>1</v>
       </c>
-      <c r="E12" s="13">
+      <c r="E12" s="41">
         <v>88000</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="42">
         <v>88000</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="110.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
+      <c r="A13" s="38">
         <v>2</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="40" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="7">
+      <c r="D13" s="39">
         <v>1</v>
       </c>
-      <c r="E13" s="13">
+      <c r="E13" s="41">
         <v>86000</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="42">
         <v>86000</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
+      <c r="A14" s="38">
         <v>3</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="C14" s="8" t="s">
+      <c r="C14" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="D14" s="7">
+      <c r="D14" s="39">
         <v>1</v>
       </c>
-      <c r="E14" s="13">
+      <c r="E14" s="41">
         <v>5500</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="42">
         <v>5500</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E15" s="3" t="s">
+      <c r="A15" s="43"/>
+      <c r="B15" s="44"/>
+      <c r="C15" s="44"/>
+      <c r="D15" s="44"/>
+      <c r="E15" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="10">
+      <c r="F15" s="45">
         <v>179500</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E16" s="3" t="s">
+      <c r="A16" s="43"/>
+      <c r="B16" s="44"/>
+      <c r="C16" s="44"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F16" s="10">
+      <c r="F16" s="45">
         <v>32310</v>
       </c>
     </row>
-    <row r="17" spans="5:6" x14ac:dyDescent="0.25">
-      <c r="E17" s="11" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="46"/>
+      <c r="B17" s="47"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="47"/>
+      <c r="E17" s="48" t="s">
         <v>26</v>
       </c>
-      <c r="F17" s="12">
+      <c r="F17" s="49">
         <f>SUM(F15:F16)</f>
         <v>211810</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1250,7 +2336,7 @@
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="3" width="45" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="17" customWidth="1"/>
@@ -1451,10 +2537,10 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <f>SUM(G12:G16)</f>
         <v>178630</v>
       </c>
@@ -1469,6 +2555,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -1477,9 +2566,9 @@
   <dimension ref="A2:G16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.85546875" customWidth="1"/>
     <col min="2" max="2" width="61.140625" customWidth="1"/>
-    <col min="3" max="3" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
     <col min="4" max="4" width="6.5703125" customWidth="1"/>
     <col min="5" max="5" width="19.140625" customWidth="1"/>
     <col min="6" max="6" width="20.85546875" customWidth="1"/>
@@ -1487,149 +2576,217 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="28"/>
+      <c r="B2" s="24"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="51" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="51" t="s">
         <v>78</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="52" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="20">
+      <c r="A4" s="53">
         <v>1</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="54" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="55" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="55">
         <v>1</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="56">
         <v>135000</v>
       </c>
-      <c r="F4" s="22">
+      <c r="F4" s="56">
         <v>130000</v>
       </c>
-      <c r="G4" s="22">
+      <c r="G4" s="57">
         <f>D4*F4</f>
         <v>130000</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="20">
+      <c r="A5" s="53">
         <v>2</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="54" t="s">
         <v>84</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="55" t="s">
         <v>85</v>
       </c>
-      <c r="D5" s="20">
+      <c r="D5" s="55">
         <v>1</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="56">
         <v>125000</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="56">
         <v>120000</v>
       </c>
-      <c r="G5" s="22">
+      <c r="G5" s="57">
         <f>D5*F5</f>
         <v>120000</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="23" t="s">
+      <c r="A6" s="25"/>
+      <c r="B6" s="58" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="24">
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="59">
         <f>SUM(G4:G5)</f>
         <v>250000</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="25"/>
+      <c r="B7" s="58" t="s">
         <v>86</v>
       </c>
-      <c r="G7" s="24">
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="59">
         <f>G6*0.18</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="23" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="25"/>
+      <c r="B8" s="58" t="s">
         <v>87</v>
       </c>
-      <c r="G8" s="25">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="60">
         <f>G6+G7</f>
         <v>295000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" thickTop="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="25"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="28"/>
+    </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B10" s="23" t="s">
+      <c r="A10" s="25"/>
+      <c r="B10" s="58" t="s">
         <v>88</v>
       </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="28"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="26" t="s">
+      <c r="A11" s="25"/>
+      <c r="B11" s="61" t="s">
         <v>89</v>
       </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="28"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B12" s="26" t="s">
+      <c r="A12" s="25"/>
+      <c r="B12" s="61" t="s">
         <v>90</v>
       </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="28"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B13" s="26" t="s">
+      <c r="A13" s="25"/>
+      <c r="B13" s="61" t="s">
         <v>91</v>
       </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="28"/>
     </row>
     <row r="14" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="27" t="s">
+      <c r="A14" s="25"/>
+      <c r="B14" s="62" t="s">
         <v>92</v>
       </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="28"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="26" t="s">
+      <c r="A15" s="25"/>
+      <c r="B15" s="61" t="s">
         <v>93</v>
       </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="28"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="26" t="s">
+      <c r="A16" s="32"/>
+      <c r="B16" s="63" t="s">
         <v>94</v>
       </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A2:B2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>